--- a/AAII_Financials/Quarterly/MPNGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MPNGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>MPNGY</t>
   </si>
@@ -656,71 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +766,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +813,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +860,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +881,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +926,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +973,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1020,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1067,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1085,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1130,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1177,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1198,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1243,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1290,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1337,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1384,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1431,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1478,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1525,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1572,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1619,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1666,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1713,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1760,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1807,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1854,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1901,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +1948,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2021,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,404 +2040,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16967200</v>
+      </c>
+      <c r="E41" s="3">
         <v>15265300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13939000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14190300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15850000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9704500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6054300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7527900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7033300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4701800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3446700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3723400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3910600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2922700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9183300</v>
+      </c>
+      <c r="E42" s="3">
         <v>8587200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5907100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9682200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9008100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13345400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13072100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10809000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12161300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15769600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14866000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12849600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12306800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13320400</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>546500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3475400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>486600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>438500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>399400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1929400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>463600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1472800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>416100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1635200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>401900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1466300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>335500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1494500</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E44" s="3">
         <v>752400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>436700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>346600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>262000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>395300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>253000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>324700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>185600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>280700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>186900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>273800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>150700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>261300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4131900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1003700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4236900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3187000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2502500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>681400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2214600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>666200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1858000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>704700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1963900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>746000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1840100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>637600</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34221400</v>
+      </c>
+      <c r="E46" s="3">
         <v>32176800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28024900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30346100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30406000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28734300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24787100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23430600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24185500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25824100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23358900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21109500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20471100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20754100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7675600</v>
+      </c>
+      <c r="E47" s="3">
         <v>6568800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6172800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6060900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6254400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6690900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6447400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6872700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6642200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6714500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7366600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7506300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7318600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6102700</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5837000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5533800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5375900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4749700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4428400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4142800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4332000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4058600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3702600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3663500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3328800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3022200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3161800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3218900</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4375600</v>
+      </c>
+      <c r="E49" s="3">
         <v>4320700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4251800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4232600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4183900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4141700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4315700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4171200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4204800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4286900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4172900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4203900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4444100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4442800</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2508,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2555,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>370300</v>
+      </c>
+      <c r="E52" s="3">
         <v>133900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>377500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>404300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>440800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>189900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>616300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>240400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>501300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>230700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>680000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>196800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>769100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2649,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53192200</v>
+      </c>
+      <c r="E54" s="3">
         <v>49598300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44672700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46092600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46018300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44437700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40762200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39295800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39513300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>41324700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39129600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36678800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36396500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35446400</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2717,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2736,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4583300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5275800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4309900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4083500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3496600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3627000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3396900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3203300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2810900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3291600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2924600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2627100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2218300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2563900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2833700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2447200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2670400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2674400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2686500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2629200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1854400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1907600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1861400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3074600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3298400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2853400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2870200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2860300</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9721500</v>
+      </c>
+      <c r="E59" s="3">
         <v>8490700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9426700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8943000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8369900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7328400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8343000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6943500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7466600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6755200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7153700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5213900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6105900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4502400</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17138500</v>
+      </c>
+      <c r="E60" s="3">
         <v>17663000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16407000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15700900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14553000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14787500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13594300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12970600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12138900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14225900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13376700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11635000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11194500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11081300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13520800</v>
+      </c>
+      <c r="E61" s="3">
         <v>9936800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4530700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4441600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5865300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5797800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4039400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4016500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5478500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5474500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5318500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5279800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5525400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5561600</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E62" s="3">
         <v>84300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>95800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>93000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>58000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>56700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>56500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3063,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3110,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3157,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31462000</v>
+      </c>
+      <c r="E66" s="3">
         <v>28011300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21161900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20366400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20643000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20790300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17914500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17209400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17805800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19895000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18870400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17093600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16868300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16785900</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3225,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3270,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3317,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3364,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3411,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24642400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-23335600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-20799300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-18068700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17879800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-19153300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-20818600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-21865800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-23578500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24766500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24371200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25015500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27093100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27470000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3505,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3552,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3599,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21738600</v>
+      </c>
+      <c r="E76" s="3">
         <v>21595300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23518900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25734400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25383400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23655400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22856100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22094100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21715300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21437800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20266800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19592800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19536300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18668700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3693,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3792,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +3813,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>298900</v>
+      </c>
+      <c r="E83" s="3">
         <v>294000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>305700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>284000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>253100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>251200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>273500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>274100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>280000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>344400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>349200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>330800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>334200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>380100</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +3905,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +3952,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +3999,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4046,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4093,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1017000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-939500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3111100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>666300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1396100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2310200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2173500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2622400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>828400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1465800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1536600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1498300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1171900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>589200</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,52 +4161,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1897300</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-716400</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
         <v>-794100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-696300</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3">
         <v>-267800</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-363700</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4253,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4300,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1035600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2891800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2920300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-773600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4789000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-880900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1701700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>720600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3231800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>152000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2082300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1345400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-115100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>198800</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,8 +4368,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4180,8 +4413,11 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4460,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4507,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,136 +4554,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3593400</v>
+      </c>
+      <c r="E100" s="3">
         <v>5008900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-135000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1861700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>69800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2322100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2131300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2827000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1644000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-458000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>296500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-156000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-82400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1239600</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E101" s="3">
         <v>134900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-84900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>22400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>65200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>76000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-75300</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1487200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1077600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-340200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2060500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6281800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3886200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1744400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>539500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2415900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1155100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-254100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>976000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-449200</v>
       </c>
     </row>
